--- a/Result/profitability/1437.xlsx
+++ b/Result/profitability/1437.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62125</v>
       </c>
       <c r="N2" t="n">
-        <v>50.135</v>
+        <v>50.4875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.18</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4725</v>
+        <v>0.58125</v>
       </c>
       <c r="N3" t="n">
-        <v>43.64375</v>
+        <v>45.925</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.45</v>
       </c>
       <c r="M4" t="n">
-        <v>0.35375</v>
+        <v>0.4825</v>
       </c>
       <c r="N4" t="n">
-        <v>37.3575</v>
+        <v>39.43125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.99</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1875</v>
+        <v>0.3812500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>28.0225</v>
+        <v>29.8975</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0.17875</v>
+        <v>0.17</v>
       </c>
       <c r="N6" t="n">
-        <v>20.89375</v>
+        <v>21.43625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002500000000000013</v>
+        <v>0.07250000000000004</v>
       </c>
       <c r="N7" t="n">
-        <v>14.50125</v>
+        <v>17.17</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.26</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.06624999999999999</v>
+        <v>0.02000000000000003</v>
       </c>
       <c r="N8" t="n">
-        <v>10.42625</v>
+        <v>11.2425</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1437</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>236</v>
+      </c>
+      <c r="D75" t="n">
+        <v>76</v>
+      </c>
+      <c r="E75" t="n">
+        <v>160</v>
+      </c>
+      <c r="F75" t="n">
+        <v>67.94</v>
+      </c>
+      <c r="G75" t="n">
+        <v>124</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>52.73%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>177</v>
+      </c>
+      <c r="J75" t="n">
+        <v>301</v>
+      </c>
+      <c r="K75" t="n">
+        <v>276</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.7300000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.014705882352941</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.530000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1063344732128317</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-8.611111111111111</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2833396297695505</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
